--- a/erp-server/erp-server-oms/src/main/resources/excel/soB2cAbnormal.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/soB2cAbnormal.xlsx
@@ -29,12 +29,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>销售订单</t>
   </si>
   <si>
     <t>平台信息</t>
+  </si>
+  <si>
+    <t>店铺</t>
   </si>
   <si>
     <t>审核状态</t>
@@ -79,6 +82,9 @@
   </si>
   <si>
     <t>{.dictPlatform}</t>
+  </si>
+  <si>
+    <t>{.shopName}</t>
   </si>
   <si>
     <t>{.approveStatusName}</t>
@@ -1048,21 +1054,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="17.875" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="16.875" customWidth="1"/>
-    <col min="4" max="5" width="17.375" customWidth="1"/>
-    <col min="6" max="7" width="14.5" customWidth="1"/>
-    <col min="8" max="8" width="17" customWidth="1"/>
-    <col min="9" max="9" width="16.25" customWidth="1"/>
-    <col min="10" max="10" width="22.75" customWidth="1"/>
-    <col min="11" max="11" width="15" customWidth="1"/>
+    <col min="3" max="4" width="16.875" customWidth="1"/>
+    <col min="5" max="6" width="17.375" customWidth="1"/>
+    <col min="7" max="8" width="14.5" customWidth="1"/>
+    <col min="9" max="9" width="17" customWidth="1"/>
+    <col min="10" max="10" width="16.25" customWidth="1"/>
+    <col min="11" max="11" width="22.75" customWidth="1"/>
+    <col min="12" max="12" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1084,10 +1090,10 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
@@ -1099,43 +1105,49 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L2" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="M2" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
